--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104536_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104536_W9.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0941</v>
+        <v>5.3153</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3818</v>
+        <v>4.5393</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7123</v>
+        <v>0.7761</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0698</v>
+        <v>3.0751</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9507</v>
+        <v>0.9616</v>
       </c>
       <c r="I2" t="n">
-        <v>2.119</v>
+        <v>2.1135</v>
       </c>
       <c r="J2" t="n">
-        <v>3.695</v>
+        <v>3.6744</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5694</v>
+        <v>2.554</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6252</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2706</v>
+        <v>-1.0557</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.113</v>
+        <v>-0.9271</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1576</v>
+        <v>-0.1286</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.162</v>
+        <v>3.2964</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4085</v>
+        <v>1.5918</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7535</v>
+        <v>1.7046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4768</v>
+        <v>1.4799</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4906</v>
+        <v>0.4938</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9862</v>
+        <v>0.9861</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8258</v>
+        <v>1.8218</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.349</v>
+        <v>-0.3419</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3563</v>
+        <v>-0.2323</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4174</v>
+        <v>-0.2301</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0611</v>
+        <v>-0.0022</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6433</v>
+        <v>1.8653</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7417</v>
+        <v>0.89</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0984</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1032</v>
+        <v>1.4812</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5601</v>
+        <v>0.8791</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6632</v>
+        <v>0.6021</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7307</v>
+        <v>2.2661</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0866</v>
+        <v>0.8511</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6441</v>
+        <v>1.415</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6275</v>
+        <v>-0.7849</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9808</v>
+        <v>-0.8129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08649999999999999</v>
+        <v>-0.871</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5989</v>
+        <v>-0.7599</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5123</v>
+        <v>-0.1111</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.4764</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>-0.6162</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4855</v>
+        <v>0.9021</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4244</v>
+        <v>1.8468</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0612</v>
+        <v>-0.9447</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4776</v>
+        <v>1.1113</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8832</v>
+        <v>-0.5464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5945</v>
+        <v>1.6577</v>
       </c>
       <c r="J5" t="n">
-        <v>2.287</v>
+        <v>2.7147</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8689</v>
+        <v>0.0862</v>
       </c>
       <c r="L5" t="n">
-        <v>1.418</v>
+        <v>2.6285</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8094</v>
+        <v>-1.6034</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0142</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8236</v>
+        <v>-0.9708</v>
       </c>
       <c r="P5" t="n">
-        <v>2.722</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2358</v>
+        <v>-0.6644</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2521</v>
+        <v>-0.2744</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0163</v>
+        <v>-0.3899</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4783</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6105</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8678</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.299</v>
+        <v>0.4781</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1224</v>
+        <v>0.3627</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1767</v>
+        <v>0.1155</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3897</v>
+        <v>0.3981</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0168</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3812</v>
+        <v>0.3813</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2999</v>
+        <v>2.2885</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9103</v>
+        <v>-1.8904</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0395</v>
+        <v>-0.8792</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0434</v>
+        <v>-0.7877</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0039</v>
+        <v>-0.0915</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2677</v>
+        <v>0.2413</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8459</v>
+        <v>-1.2296</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1136</v>
+        <v>1.4708</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3328</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.418</v>
+        <v>0.9732</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0852</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7761</v>
+        <v>-0.7207</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9994</v>
+        <v>0.0689</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2233</v>
+        <v>-0.7896</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5567</v>
+        <v>0.7912</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5814</v>
+        <v>0.9043</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1381</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2683</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.4025</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9893</v>
+        <v>-1.1951</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2571</v>
+        <v>-0.5089</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7322</v>
+        <v>-0.6862</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1123</v>
+        <v>-0.0206</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4127</v>
+        <v>-2.19</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3004</v>
+        <v>2.1694</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0616</v>
+        <v>-1.3662</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9651999999999999</v>
+        <v>-1.4433</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9036</v>
+        <v>0.0771</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7171</v>
+        <v>-0.8259</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0693</v>
+        <v>-2.0317</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7864</v>
+        <v>1.2058</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7786999999999999</v>
+        <v>-0.5403</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8959</v>
+        <v>0.5884</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1172</v>
+        <v>-1.1287</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>3.4145</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5349</v>
+        <v>-1.2462</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6956</v>
+        <v>-0.5415</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8393</v>
+        <v>-0.7047</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5754</v>
+        <v>-0.5085</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.7927</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3839</v>
+        <v>0.2842</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8359</v>
+        <v>0.8456</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6839</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.152</v>
+        <v>0.1566</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0512</v>
+        <v>1.0425</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2153</v>
+        <v>-0.1968</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8641</v>
+        <v>0.8754</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4112</v>
+        <v>-1.3541</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8347</v>
+        <v>-0.6483</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5765</v>
+        <v>-0.7058</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9107</v>
+        <v>-2.4527</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6621</v>
+        <v>-4.2629</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7513</v>
+        <v>1.8103</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.988</v>
+        <v>-1.9824</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6485</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6256</v>
+        <v>-2.6309</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4845</v>
+        <v>-2.5043</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.802</v>
+        <v>-1.818</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4965</v>
+        <v>0.5219</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3201</v>
+        <v>1.3347</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8301</v>
+        <v>-1.3808</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0434</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7867</v>
+        <v>-0.7603</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9239</v>
+        <v>-2.5161</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0867</v>
+        <v>-3.8513</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1628</v>
+        <v>1.3352</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9769</v>
+        <v>-1.9842</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6175</v>
+        <v>-0.6257</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3594</v>
+        <v>-1.3585</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2569</v>
+        <v>-2.274</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5452</v>
+        <v>-1.5588</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.28</v>
+        <v>0.2898</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9277</v>
+        <v>0.9331</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5349</v>
+        <v>-1.1254</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6956</v>
+        <v>-0.4392</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8393</v>
+        <v>-0.6862</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8264</v>
+        <v>-4.9445</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8967</v>
+        <v>-5.9236</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0703</v>
+        <v>0.979</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1417</v>
+        <v>-4.1353</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8829</v>
+        <v>0.8954</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.0246</v>
+        <v>-5.0307</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5565</v>
+        <v>-3.5809</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.6706</v>
+        <v>-3.6876</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.5544</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7688</v>
+        <v>0.7887</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9212</v>
+        <v>-1.029</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5353</v>
+        <v>-0.5138</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3859</v>
+        <v>-0.5152</v>
       </c>
       <c r="V12" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6029</v>
+        <v>1.6561</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.7845</v>
+        <v>-9.019500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>10.3876</v>
+        <v>10.6757</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0248</v>
+        <v>-1.006400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.906999999999999</v>
+        <v>2.942</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.9319</v>
+        <v>-3.9484</v>
       </c>
       <c r="J13" t="n">
-        <v>4.0985</v>
+        <v>3.902199999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4849</v>
+        <v>-1.5748</v>
       </c>
       <c r="L13" t="n">
-        <v>5.583299999999998</v>
+        <v>5.477100000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.1234</v>
+        <v>-4.908500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3916</v>
+        <v>4.5168</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.5153</v>
+        <v>-9.4253</v>
       </c>
       <c r="P13" t="n">
-        <v>12.4758</v>
+        <v>12.5199</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.476</v>
+        <v>-12.5199</v>
       </c>
       <c r="R13" t="n">
-        <v>24.9516</v>
+        <v>25.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.0373</v>
+        <v>-11.0332</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.2887</v>
+        <v>-6.251399999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.7485</v>
+        <v>-4.781700000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1892</v>
+        <v>1.1758</v>
       </c>
       <c r="W13" t="n">
-        <v>5.8813</v>
+        <v>5.8492</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.6921</v>
+        <v>-4.673399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9388</v>
+        <v>5.7526</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5412</v>
+        <v>4.1125</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3976</v>
+        <v>1.6401</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7678</v>
+        <v>3.7652</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7531</v>
+        <v>0.758</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0147</v>
+        <v>3.0072</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9404</v>
+        <v>3.9199</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0919</v>
+        <v>3.0753</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1726</v>
+        <v>-0.1548</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1461</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1724</v>
+        <v>0.4202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3185</v>
+        <v>0.538</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0409</v>
+        <v>1.5014</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0864</v>
+        <v>-0.3407</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9545</v>
+        <v>1.8421</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4356</v>
+        <v>0.433</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8065</v>
+        <v>-0.8125</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2422</v>
+        <v>1.2455</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0871</v>
+        <v>-0.0989</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7588</v>
+        <v>-0.7692</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5228</v>
+        <v>0.5319</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8321</v>
+        <v>1.2961</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3077</v>
+        <v>0.8964</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5244</v>
+        <v>0.3997</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7784</v>
+        <v>1.4361</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6957</v>
+        <v>-1.1865</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4741</v>
+        <v>2.6227</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2496</v>
+        <v>0.249</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4083</v>
+        <v>-1.4074</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6579</v>
+        <v>1.6564</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5959</v>
+        <v>-0.6148</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8455</v>
+        <v>0.8638</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.638</v>
+        <v>1.2961</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2612</v>
+        <v>0.794</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3768</v>
+        <v>0.5021</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7129</v>
+        <v>0.9774</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8898</v>
+        <v>0.1665</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8109</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6975</v>
+        <v>1.7033</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7907</v>
+        <v>1.7894</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0861</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3687</v>
+        <v>2.3595</v>
       </c>
       <c r="K17" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6712</v>
+        <v>-0.6562</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6033</v>
+        <v>0.8675</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0162</v>
+        <v>0.311</v>
       </c>
       <c r="U17" t="n">
-        <v>0.587</v>
+        <v>0.5565</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1644</v>
+        <v>0.5399</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8722</v>
+        <v>-1.302</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0366</v>
+        <v>1.842</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1981</v>
+        <v>-0.1887</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4993</v>
+        <v>-0.4943</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3012</v>
+        <v>0.3056</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.14</v>
+        <v>-0.1498</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0581</v>
+        <v>-0.0389</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7401</v>
+        <v>1.1139</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3297</v>
+        <v>0.2622</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0697</v>
+        <v>0.8517</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4227</v>
+        <v>-0.1272</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6622</v>
+        <v>0.9151</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0849</v>
+        <v>-1.0423</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0608</v>
+        <v>0.4743</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4877</v>
+        <v>0.5488</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.0745</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7117</v>
+        <v>1.0872</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7864</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.9977</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.349</v>
+        <v>-0.6129</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2986</v>
+        <v>0.4593</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.0722</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7473</v>
+        <v>0.5075</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5081</v>
+        <v>0.0556</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2392</v>
+        <v>0.452</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1093</v>
+        <v>-1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2019</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5132</v>
+        <v>-0.2819</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4574</v>
+        <v>-0.8964</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9707</v>
+        <v>0.6145</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4781</v>
+        <v>-1.1529</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5527</v>
+        <v>-0.5199</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0746</v>
+        <v>-0.633</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1016</v>
+        <v>-1.1401</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0968</v>
+        <v>-0.4621</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0048</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6236</v>
+        <v>-0.0129</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4559</v>
+        <v>-0.0578</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1279</v>
+        <v>0.6434</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>0.2437</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5453</v>
+        <v>0.3997</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5978</v>
+        <v>-0.6841</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1812</v>
+        <v>0.4206</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5834</v>
+        <v>-1.1047</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8428</v>
+        <v>-1.0571</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0273</v>
+        <v>-0.4882</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8156</v>
+        <v>-0.5688</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1506</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0733</v>
+        <v>-0.7896</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2239</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9935</v>
+        <v>-0.3419</v>
       </c>
       <c r="N21" t="n">
-        <v>0.046</v>
+        <v>0.3014</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0395</v>
+        <v>-0.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8348</v>
+        <v>0.4819</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7512</v>
+        <v>0.2739</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0836</v>
+        <v>0.208</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3214</v>
+        <v>-0.1089</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8678</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0023</v>
+        <v>-1.2838</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4796</v>
+        <v>-3.5509</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4773</v>
+        <v>2.2671</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1553</v>
+        <v>-0.118</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5209</v>
+        <v>-0.9359</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6344</v>
+        <v>0.8179</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1317</v>
+        <v>-1.0107</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4573</v>
+        <v>-1.5243</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6744</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0236</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0636</v>
+        <v>0.5884</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04</v>
+        <v>0.3043</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0738</v>
+        <v>1.13</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>0.5571</v>
       </c>
       <c r="U22" t="n">
-        <v>0.274</v>
+        <v>0.5729</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4358</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5398</v>
+        <v>-1.7474</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7562</v>
+        <v>-2.2735</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2165</v>
+        <v>0.5262</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1135</v>
+        <v>-0.8407</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9292</v>
+        <v>-0.0368</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8157</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9908</v>
+        <v>0.1298</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5106</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.2234</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8773</v>
+        <v>-0.9704</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5814</v>
+        <v>0.0568</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2959</v>
+        <v>-1.0273</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.722</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8586</v>
+        <v>1.6852</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3176</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5411</v>
+        <v>0.9911</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4371</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1093</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4933</v>
+        <v>-2.5191</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1104</v>
+        <v>-3.1092</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6171</v>
+        <v>0.59</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.975</v>
+        <v>-0.9906</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4125</v>
+        <v>-0.4244</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5625</v>
+        <v>-0.5662</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5999</v>
+        <v>-0.6248</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2233</v>
+        <v>1.2058</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5984</v>
+        <v>-1.5717</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7858</v>
+        <v>-1.772</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4966</v>
+        <v>1.5006</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6775</v>
+        <v>0.3875</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1741</v>
+        <v>1.1131</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6693</v>
+        <v>-4.1746</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9293</v>
+        <v>-3.6312</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.74</v>
+        <v>-0.5434</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.2584</v>
+        <v>-1.2705</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.9187</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3466</v>
+        <v>-0.3518</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5959</v>
+        <v>0.5606</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2233</v>
+        <v>1.2058</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8543</v>
+        <v>-1.831</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0862</v>
+        <v>0.5982</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U25" t="n">
-        <v>0.555</v>
+        <v>0.7123</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W25" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.602999999999998</v>
+        <v>-0.6106999999999996</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.3876</v>
+        <v>-10.6757</v>
       </c>
       <c r="F26" t="n">
-        <v>9.784599999999999</v>
+        <v>10.0652</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0247</v>
+        <v>1.0063</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.907</v>
+        <v>-2.9419</v>
       </c>
       <c r="I26" t="n">
-        <v>3.931699999999999</v>
+        <v>3.948300000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>5.1235</v>
+        <v>4.908600000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.3919</v>
+        <v>-4.5167</v>
       </c>
       <c r="L26" t="n">
-        <v>9.5151</v>
+        <v>9.4252</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.0987</v>
+        <v>-3.902400000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4848</v>
+        <v>1.5747</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.583400000000001</v>
+        <v>-5.476999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-12.4758</v>
+        <v>-12.5196</v>
       </c>
       <c r="Q26" t="n">
-        <v>-24.9516</v>
+        <v>-25.0394</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4756</v>
+        <v>12.5196</v>
       </c>
       <c r="S26" t="n">
-        <v>12.0372</v>
+        <v>12.0786</v>
       </c>
       <c r="T26" t="n">
-        <v>4.748399999999999</v>
+        <v>4.7816</v>
       </c>
       <c r="U26" t="n">
-        <v>7.2887</v>
+        <v>7.2971</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.1892</v>
+        <v>-1.1756</v>
       </c>
       <c r="W26" t="n">
-        <v>4.6922</v>
+        <v>4.6734</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.8814</v>
+        <v>-5.848999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104536_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104536_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.673399999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104536_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.848999999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
